--- a/results/Results.xlsx
+++ b/results/Results.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10531"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="4457" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F8834F75-069A-4AEB-9F3B-D6E9B7797487}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hirofumi.tanahashi/ResearchProject/app-feature-extraction-llm/results/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746C41A4-D003-5B47-9D06-F11F47F07365}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1200" yWindow="780" windowWidth="28960" windowHeight="20060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="results (in-domain)" sheetId="22" r:id="rId1"/>
@@ -180,7 +185,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,15 +777,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD303C8D-48E4-4A9A-AA19-0B567ABB060A}">
   <dimension ref="A1:M79"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28" style="5" customWidth="1"/>
-    <col min="2" max="2" width="21.140625" style="5" customWidth="1"/>
-    <col min="3" max="13" width="8.42578125" style="5" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="2" max="2" width="21.1640625" style="5" customWidth="1"/>
+    <col min="3" max="13" width="8.5" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="37"/>
       <c r="B1" s="38" t="s">
         <v>0</v>
@@ -819,7 +824,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" s="2" customFormat="1">
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
         <v>12</v>
       </c>
@@ -858,7 +863,7 @@
       </c>
       <c r="M2" s="29"/>
     </row>
-    <row r="3" spans="1:13" s="2" customFormat="1">
+    <row r="3" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="23"/>
       <c r="B3" s="3" t="s">
         <v>14</v>
@@ -895,7 +900,7 @@
       </c>
       <c r="M3" s="33"/>
     </row>
-    <row r="4" spans="1:13" s="2" customFormat="1">
+    <row r="4" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>15</v>
       </c>
@@ -937,7 +942,7 @@
         <v>0.57465489999999986</v>
       </c>
     </row>
-    <row r="5" spans="1:13" s="2" customFormat="1">
+    <row r="5" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="3" t="s">
         <v>17</v>
@@ -977,7 +982,7 @@
         <v>0.41941980000000012</v>
       </c>
     </row>
-    <row r="6" spans="1:13" s="2" customFormat="1">
+    <row r="6" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="24"/>
       <c r="B6" s="28" t="s">
         <v>18</v>
@@ -1017,7 +1022,7 @@
         <v>0.48529989999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:13" s="2" customFormat="1">
+    <row r="7" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="21" t="s">
         <v>19</v>
       </c>
@@ -1059,7 +1064,7 @@
         <v>0.63094829999999991</v>
       </c>
     </row>
-    <row r="8" spans="1:13" s="2" customFormat="1">
+    <row r="8" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="23"/>
       <c r="B8" s="3" t="s">
         <v>17</v>
@@ -1099,7 +1104,7 @@
         <v>0.57226450000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:13" s="2" customFormat="1">
+    <row r="9" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="24"/>
       <c r="B9" s="28" t="s">
         <v>18</v>
@@ -1139,7 +1144,7 @@
         <v>0.60040500000000008</v>
       </c>
     </row>
-    <row r="10" spans="1:13" s="2" customFormat="1">
+    <row r="10" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>20</v>
       </c>
@@ -1177,11 +1182,11 @@
         <v>0.37309999999999999</v>
       </c>
       <c r="M10" s="30">
-        <f t="shared" ref="M10:M12" si="1">AVERAGE(C10:L10)</f>
+        <f t="shared" ref="M10:M11" si="1">AVERAGE(C10:L10)</f>
         <v>0.32728999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:13" s="2" customFormat="1">
+    <row r="11" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="23"/>
       <c r="B11" s="3" t="s">
         <v>17</v>
@@ -1221,7 +1226,7 @@
         <v>0.40655000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="2" customFormat="1">
+    <row r="12" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="25"/>
       <c r="B12" s="22" t="s">
         <v>18</v>
@@ -1261,7 +1266,7 @@
         <v>0.36040000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:13" s="2" customFormat="1">
+    <row r="13" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="23" t="s">
         <v>21</v>
       </c>
@@ -1299,11 +1304,11 @@
         <v>0.81259999999999999</v>
       </c>
       <c r="M13" s="31">
-        <f t="shared" ref="M13:M15" si="2">AVERAGE(C13:L13)</f>
+        <f t="shared" ref="M13:M14" si="2">AVERAGE(C13:L13)</f>
         <v>0.73126999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="2" customFormat="1">
+    <row r="14" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="23"/>
       <c r="B14" s="3" t="s">
         <v>17</v>
@@ -1343,7 +1348,7 @@
         <v>0.72410000000000008</v>
       </c>
     </row>
-    <row r="15" spans="1:13" s="2" customFormat="1">
+    <row r="15" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="24"/>
       <c r="B15" s="28" t="s">
         <v>18</v>
@@ -1383,7 +1388,7 @@
         <v>0.72755999999999998</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="2" customFormat="1">
+    <row r="16" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>22</v>
       </c>
@@ -1421,11 +1426,11 @@
         <v>0.63160000000000005</v>
       </c>
       <c r="M16" s="30">
-        <f t="shared" ref="M16:M18" si="3">AVERAGE(C16:L16)</f>
+        <f t="shared" ref="M16:M17" si="3">AVERAGE(C16:L16)</f>
         <v>0.57238</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="2" customFormat="1">
+    <row r="17" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="23"/>
       <c r="B17" s="3" t="s">
         <v>17</v>
@@ -1465,7 +1470,7 @@
         <v>2.4980000000000002E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="2" customFormat="1">
+    <row r="18" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="24"/>
       <c r="B18" s="28" t="s">
         <v>23</v>
@@ -1505,7 +1510,7 @@
         <v>4.7600000000000003E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:13" s="2" customFormat="1">
+    <row r="19" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="21" t="s">
         <v>24</v>
       </c>
@@ -1543,11 +1548,11 @@
         <v>0.64249999999999996</v>
       </c>
       <c r="M19" s="30">
-        <f t="shared" ref="M19:M21" si="4">AVERAGE(C19:L19)</f>
+        <f t="shared" ref="M19:M20" si="4">AVERAGE(C19:L19)</f>
         <v>0.60843000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="2" customFormat="1">
+    <row r="20" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="23"/>
       <c r="B20" s="3" t="s">
         <v>17</v>
@@ -1587,7 +1592,7 @@
         <v>0.60566999999999993</v>
       </c>
     </row>
-    <row r="21" spans="1:13" s="2" customFormat="1">
+    <row r="21" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="24"/>
       <c r="B21" s="28" t="s">
         <v>23</v>
@@ -1627,7 +1632,7 @@
         <v>0.60703999999999991</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="2" customFormat="1">
+    <row r="22" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
         <v>25</v>
       </c>
@@ -1665,11 +1670,11 @@
         <v>0.3165</v>
       </c>
       <c r="M22" s="30">
-        <f t="shared" ref="M22:M24" si="5">AVERAGE(C22:L22)</f>
+        <f t="shared" ref="M22:M23" si="5">AVERAGE(C22:L22)</f>
         <v>0.24290000000000003</v>
       </c>
     </row>
-    <row r="23" spans="1:13" s="2" customFormat="1">
+    <row r="23" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="23"/>
       <c r="B23" s="3" t="s">
         <v>17</v>
@@ -1709,7 +1714,7 @@
         <v>0.19650999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="2" customFormat="1">
+    <row r="24" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="24"/>
       <c r="B24" s="28" t="s">
         <v>23</v>
@@ -1749,7 +1754,7 @@
         <v>0.21370999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:13" s="2" customFormat="1">
+    <row r="25" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="21" t="s">
         <v>26</v>
       </c>
@@ -1787,11 +1792,11 @@
         <v>0.65710000000000002</v>
       </c>
       <c r="M25" s="30">
-        <f t="shared" ref="M25:M27" si="6">AVERAGE(C25:L25)</f>
+        <f t="shared" ref="M25:M26" si="6">AVERAGE(C25:L25)</f>
         <v>0.56185999999999992</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="2" customFormat="1">
+    <row r="26" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="23"/>
       <c r="B26" s="3" t="s">
         <v>17</v>
@@ -1831,7 +1836,7 @@
         <v>0.56048000000000009</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="2" customFormat="1">
+    <row r="27" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="24"/>
       <c r="B27" s="28" t="s">
         <v>23</v>
@@ -1871,7 +1876,7 @@
         <v>0.56114999999999993</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="2" customFormat="1">
+    <row r="28" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="21" t="s">
         <v>27</v>
       </c>
@@ -1909,11 +1914,11 @@
         <v>0.4194</v>
       </c>
       <c r="M28" s="30">
-        <f t="shared" ref="M28:M30" si="7">AVERAGE(C28:L28)</f>
+        <f t="shared" ref="M28:M29" si="7">AVERAGE(C28:L28)</f>
         <v>0.37975999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:13" s="2" customFormat="1">
+    <row r="29" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="23"/>
       <c r="B29" s="3" t="s">
         <v>17</v>
@@ -1953,7 +1958,7 @@
         <v>0.39208999999999994</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="2" customFormat="1">
+    <row r="30" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="24"/>
       <c r="B30" s="28" t="s">
         <v>23</v>
@@ -1993,7 +1998,7 @@
         <v>0.38392999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="2" customFormat="1">
+    <row r="31" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="21" t="s">
         <v>28</v>
       </c>
@@ -2031,11 +2036,11 @@
         <v>0.56859999999999999</v>
       </c>
       <c r="M31" s="30">
-        <f t="shared" ref="M31:M33" si="8">AVERAGE(C31:L31)</f>
+        <f t="shared" ref="M31:M32" si="8">AVERAGE(C31:L31)</f>
         <v>0.58222999999999991</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="2" customFormat="1">
+    <row r="32" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="23"/>
       <c r="B32" s="3" t="s">
         <v>17</v>
@@ -2075,7 +2080,7 @@
         <v>0.58018999999999998</v>
       </c>
     </row>
-    <row r="33" spans="1:13" s="2" customFormat="1">
+    <row r="33" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="25"/>
       <c r="B33" s="22" t="s">
         <v>23</v>
@@ -2115,7 +2120,7 @@
         <v>0.58120000000000016</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="2" customFormat="1">
+    <row r="34" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="23" t="s">
         <v>29</v>
       </c>
@@ -2157,7 +2162,7 @@
         <v>0.32500000000000007</v>
       </c>
     </row>
-    <row r="35" spans="1:13" s="2" customFormat="1">
+    <row r="35" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="23"/>
       <c r="B35" s="3" t="s">
         <v>17</v>
@@ -2197,7 +2202,7 @@
         <v>0.41420999999999991</v>
       </c>
     </row>
-    <row r="36" spans="1:13" s="2" customFormat="1">
+    <row r="36" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="24"/>
       <c r="B36" s="28" t="s">
         <v>23</v>
@@ -2237,7 +2242,7 @@
         <v>0.36315999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="2" customFormat="1">
+    <row r="37" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="21" t="s">
         <v>30</v>
       </c>
@@ -2275,11 +2280,11 @@
         <v>0.48509999999999998</v>
       </c>
       <c r="M37" s="30">
-        <f t="shared" ref="M37:M39" si="10">AVERAGE(C37:L37)</f>
+        <f t="shared" ref="M37:M38" si="10">AVERAGE(C37:L37)</f>
         <v>0.54519000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:13" s="2" customFormat="1">
+    <row r="38" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="23"/>
       <c r="B38" s="3" t="s">
         <v>17</v>
@@ -2319,7 +2324,7 @@
         <v>0.54559000000000002</v>
       </c>
     </row>
-    <row r="39" spans="1:13" s="2" customFormat="1">
+    <row r="39" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="24"/>
       <c r="B39" s="28" t="s">
         <v>23</v>
@@ -2359,7 +2364,7 @@
         <v>0.54539000000000004</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="2" customFormat="1">
+    <row r="40" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="21" t="s">
         <v>31</v>
       </c>
@@ -2397,11 +2402,11 @@
         <v>0.31409999999999999</v>
       </c>
       <c r="M40" s="30">
-        <f t="shared" ref="M40:M42" si="11">AVERAGE(C40:L40)</f>
+        <f t="shared" ref="M40:M41" si="11">AVERAGE(C40:L40)</f>
         <v>0.28993999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:13" s="2" customFormat="1">
+    <row r="41" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="23"/>
       <c r="B41" s="3" t="s">
         <v>17</v>
@@ -2441,7 +2446,7 @@
         <v>0.25278</v>
       </c>
     </row>
-    <row r="42" spans="1:13" s="2" customFormat="1">
+    <row r="42" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="24"/>
       <c r="B42" s="28" t="s">
         <v>23</v>
@@ -2481,7 +2486,7 @@
         <v>0.26650000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:13" s="2" customFormat="1">
+    <row r="43" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="21" t="s">
         <v>32</v>
       </c>
@@ -2519,11 +2524,11 @@
         <v>0.60940000000000005</v>
       </c>
       <c r="M43" s="30">
-        <f t="shared" ref="M43:M45" si="12">AVERAGE(C43:L43)</f>
+        <f t="shared" ref="M43:M44" si="12">AVERAGE(C43:L43)</f>
         <v>0.58660999999999996</v>
       </c>
     </row>
-    <row r="44" spans="1:13" s="2" customFormat="1">
+    <row r="44" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="23"/>
       <c r="B44" s="3" t="s">
         <v>17</v>
@@ -2563,7 +2568,7 @@
         <v>0.58745000000000003</v>
       </c>
     </row>
-    <row r="45" spans="1:13" s="2" customFormat="1">
+    <row r="45" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="24"/>
       <c r="B45" s="28" t="s">
         <v>23</v>
@@ -2603,7 +2608,7 @@
         <v>0.58703000000000005</v>
       </c>
     </row>
-    <row r="46" spans="1:13" s="2" customFormat="1">
+    <row r="46" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="21" t="s">
         <v>33</v>
       </c>
@@ -2641,11 +2646,11 @@
         <v>0.3105</v>
       </c>
       <c r="M46" s="30">
-        <f t="shared" ref="M46:M48" si="13">AVERAGE(C46:L46)</f>
+        <f t="shared" ref="M46:M47" si="13">AVERAGE(C46:L46)</f>
         <v>0.30562000000000006</v>
       </c>
     </row>
-    <row r="47" spans="1:13" s="2" customFormat="1">
+    <row r="47" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="23"/>
       <c r="B47" s="3" t="s">
         <v>17</v>
@@ -2685,7 +2690,7 @@
         <v>0.33880999999999994</v>
       </c>
     </row>
-    <row r="48" spans="1:13" s="2" customFormat="1">
+    <row r="48" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="24"/>
       <c r="B48" s="28" t="s">
         <v>23</v>
@@ -2725,7 +2730,7 @@
         <v>0.32084999999999997</v>
       </c>
     </row>
-    <row r="49" spans="1:13" s="2" customFormat="1">
+    <row r="49" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="21" t="s">
         <v>34</v>
       </c>
@@ -2763,11 +2768,11 @@
         <v>0.50600000000000001</v>
       </c>
       <c r="M49" s="30">
-        <f t="shared" ref="M49:M51" si="14">AVERAGE(C49:L49)</f>
+        <f t="shared" ref="M49:M50" si="14">AVERAGE(C49:L49)</f>
         <v>0.52664000000000011</v>
       </c>
     </row>
-    <row r="50" spans="1:13" s="2" customFormat="1">
+    <row r="50" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="23"/>
       <c r="B50" s="3" t="s">
         <v>17</v>
@@ -2807,7 +2812,7 @@
         <v>0.52443000000000006</v>
       </c>
     </row>
-    <row r="51" spans="1:13" s="2" customFormat="1">
+    <row r="51" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="24"/>
       <c r="B51" s="28" t="s">
         <v>23</v>
@@ -2847,7 +2852,7 @@
         <v>0.52551999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:13" s="2" customFormat="1">
+    <row r="52" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="21" t="s">
         <v>35</v>
       </c>
@@ -2885,11 +2890,11 @@
         <v>0.35339999999999999</v>
       </c>
       <c r="M52" s="30">
-        <f t="shared" ref="M52:M54" si="15">AVERAGE(C52:L52)</f>
+        <f t="shared" ref="M52:M53" si="15">AVERAGE(C52:L52)</f>
         <v>0.32294999999999996</v>
       </c>
     </row>
-    <row r="53" spans="1:13" s="2" customFormat="1">
+    <row r="53" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="23"/>
       <c r="B53" s="3" t="s">
         <v>17</v>
@@ -2929,7 +2934,7 @@
         <v>0.40992999999999996</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="2" customFormat="1">
+    <row r="54" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="24"/>
       <c r="B54" s="28" t="s">
         <v>23</v>
@@ -2969,7 +2974,7 @@
         <v>0.36036000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:13" s="2" customFormat="1">
+    <row r="55" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="21" t="s">
         <v>36</v>
       </c>
@@ -3007,11 +3012,11 @@
         <v>0.46</v>
       </c>
       <c r="M55" s="30">
-        <f t="shared" ref="M55:M57" si="16">AVERAGE(C55:L55)</f>
+        <f t="shared" ref="M55:M56" si="16">AVERAGE(C55:L55)</f>
         <v>0.56642000000000003</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="2" customFormat="1">
+    <row r="56" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="23"/>
       <c r="B56" s="3" t="s">
         <v>17</v>
@@ -3051,7 +3056,7 @@
         <v>0.56442999999999999</v>
       </c>
     </row>
-    <row r="57" spans="1:13" s="2" customFormat="1">
+    <row r="57" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="24"/>
       <c r="B57" s="28" t="s">
         <v>23</v>
@@ -3091,7 +3096,7 @@
         <v>0.56540000000000012</v>
       </c>
     </row>
-    <row r="58" spans="1:13" s="2" customFormat="1">
+    <row r="58" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="15" t="s">
         <v>37</v>
       </c>
@@ -3129,11 +3134,11 @@
         <v>0.81379999999999997</v>
       </c>
       <c r="M58" s="30">
-        <f t="shared" ref="M58:M60" si="17">AVERAGE(C58:L58)</f>
+        <f t="shared" ref="M58:M59" si="17">AVERAGE(C58:L58)</f>
         <v>0.69603999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:13" s="2" customFormat="1">
+    <row r="59" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="23"/>
       <c r="B59" s="3" t="s">
         <v>17</v>
@@ -3173,7 +3178,7 @@
         <v>0.71629000000000009</v>
       </c>
     </row>
-    <row r="60" spans="1:13" s="2" customFormat="1">
+    <row r="60" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="26"/>
       <c r="B60" s="28" t="s">
         <v>23</v>
@@ -3213,7 +3218,7 @@
         <v>0.70521999999999996</v>
       </c>
     </row>
-    <row r="61" spans="1:13" s="2" customFormat="1">
+    <row r="61" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="15" t="s">
         <v>38</v>
       </c>
@@ -3251,11 +3256,11 @@
         <v>0.75439999999999996</v>
       </c>
       <c r="M61" s="30">
-        <f t="shared" ref="M61:M63" si="18">AVERAGE(C61:L61)</f>
+        <f t="shared" ref="M61:M62" si="18">AVERAGE(C61:L61)</f>
         <v>0.66657999999999995</v>
       </c>
     </row>
-    <row r="62" spans="1:13" s="2" customFormat="1">
+    <row r="62" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="23"/>
       <c r="B62" s="3" t="s">
         <v>17</v>
@@ -3295,7 +3300,7 @@
         <v>0.69990000000000019</v>
       </c>
     </row>
-    <row r="63" spans="1:13" s="2" customFormat="1">
+    <row r="63" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="26"/>
       <c r="B63" s="28" t="s">
         <v>23</v>
@@ -3335,7 +3340,7 @@
         <v>0.68153999999999992</v>
       </c>
     </row>
-    <row r="64" spans="1:13" s="2" customFormat="1">
+    <row r="64" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="15" t="s">
         <v>39</v>
       </c>
@@ -3373,11 +3378,11 @@
         <v>0.67490000000000006</v>
       </c>
       <c r="M64" s="30">
-        <f t="shared" ref="M64:M66" si="19">AVERAGE(C64:L64)</f>
+        <f t="shared" ref="M64:M65" si="19">AVERAGE(C64:L64)</f>
         <v>0.55423999999999995</v>
       </c>
     </row>
-    <row r="65" spans="1:13" s="2" customFormat="1">
+    <row r="65" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="23"/>
       <c r="B65" s="3" t="s">
         <v>17</v>
@@ -3417,7 +3422,7 @@
         <v>0.57408000000000003</v>
       </c>
     </row>
-    <row r="66" spans="1:13" s="2" customFormat="1">
+    <row r="66" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="27"/>
       <c r="B66" s="22" t="s">
         <v>23</v>
@@ -3457,7 +3462,7 @@
         <v>0.56384000000000012</v>
       </c>
     </row>
-    <row r="67" spans="1:13" s="2" customFormat="1">
+    <row r="67" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="21" t="s">
         <v>40</v>
       </c>
@@ -3495,11 +3500,11 @@
         <v>0.80900000000000005</v>
       </c>
       <c r="M67" s="30">
-        <f t="shared" ref="M67:M69" si="20">AVERAGE(C67:L67)</f>
+        <f t="shared" ref="M67:M68" si="20">AVERAGE(C67:L67)</f>
         <v>0.73070000000000002</v>
       </c>
     </row>
-    <row r="68" spans="1:13" s="2" customFormat="1">
+    <row r="68" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="23"/>
       <c r="B68" s="3" t="s">
         <v>17</v>
@@ -3539,13 +3544,13 @@
         <v>0.72950000000000004</v>
       </c>
     </row>
-    <row r="69" spans="1:13" s="2" customFormat="1">
+    <row r="69" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="26"/>
       <c r="B69" s="28" t="s">
         <v>23</v>
       </c>
       <c r="C69" s="16">
-        <v>0.72740000000000005</v>
+        <v>0.73870000000000002</v>
       </c>
       <c r="D69" s="17">
         <v>0.72340000000000004</v>
@@ -3576,10 +3581,10 @@
       </c>
       <c r="M69" s="34">
         <f>AVERAGE(C69:L69)</f>
-        <v>0.72896000000000005</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" s="2" customFormat="1">
+        <v>0.73009000000000002</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="21" t="s">
         <v>41</v>
       </c>
@@ -3617,11 +3622,11 @@
         <v>0.8054</v>
       </c>
       <c r="M70" s="30">
-        <f t="shared" ref="M70:M72" si="21">AVERAGE(C70:L70)</f>
+        <f t="shared" ref="M70:M71" si="21">AVERAGE(C70:L70)</f>
         <v>0.7159899999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:13" s="2" customFormat="1">
+    <row r="71" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="23"/>
       <c r="B71" s="3" t="s">
         <v>17</v>
@@ -3661,7 +3666,7 @@
         <v>0.71611999999999987</v>
       </c>
     </row>
-    <row r="72" spans="1:13" s="2" customFormat="1">
+    <row r="72" spans="1:13" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="27"/>
       <c r="B72" s="22" t="s">
         <v>23</v>
@@ -3701,22 +3706,22 @@
         <v>0.71604999999999985</v>
       </c>
     </row>
-    <row r="73" spans="1:13">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B73" s="36"/>
     </row>
-    <row r="75" spans="1:13">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B75" s="3"/>
     </row>
-    <row r="76" spans="1:13">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B76" s="3"/>
     </row>
-    <row r="77" spans="1:13">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B77" s="3"/>
     </row>
-    <row r="78" spans="1:13">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B78" s="3"/>
     </row>
-    <row r="79" spans="1:13">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B79" s="4"/>
     </row>
   </sheetData>
@@ -3728,5 +3733,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B06F94-AB1E-401F-AA42-E56BDC8497E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83B06F94-AB1E-401F-AA42-E56BDC8497E6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>